--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487508_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487508_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>8.6379</v>
+        <v>7.5265</v>
       </c>
       <c r="E2" t="n">
-        <v>5.1207</v>
+        <v>4.4637</v>
       </c>
       <c r="F2" t="n">
-        <v>3.5172</v>
+        <v>3.0628</v>
       </c>
       <c r="G2" t="n">
         <v>2.8379</v>
@@ -610,13 +610,13 @@
         <v>2.1543</v>
       </c>
       <c r="S2" t="n">
-        <v>1.959</v>
+        <v>0.8477</v>
       </c>
       <c r="T2" t="n">
-        <v>0.6099</v>
+        <v>-0.0471</v>
       </c>
       <c r="U2" t="n">
-        <v>1.3491</v>
+        <v>0.8947000000000001</v>
       </c>
       <c r="V2" t="n">
         <v>1.8825</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>3.2472</v>
+        <v>3.2102</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8873</v>
+        <v>0.9038</v>
       </c>
       <c r="F3" t="n">
-        <v>2.3599</v>
+        <v>2.3065</v>
       </c>
       <c r="G3" t="n">
         <v>3.1788</v>
@@ -688,13 +688,13 @@
         <v>2.3502</v>
       </c>
       <c r="S3" t="n">
-        <v>0.202</v>
+        <v>0.165</v>
       </c>
       <c r="T3" t="n">
-        <v>-0.2506</v>
+        <v>-0.2341</v>
       </c>
       <c r="U3" t="n">
-        <v>0.4525</v>
+        <v>0.3991</v>
       </c>
       <c r="V3" t="n">
         <v>1.8249</v>
@@ -721,13 +721,13 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>1.575</v>
+        <v>2.203</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.5571</v>
+        <v>-0.2765</v>
       </c>
       <c r="F4" t="n">
-        <v>2.1321</v>
+        <v>2.4796</v>
       </c>
       <c r="G4" t="n">
         <v>0.7</v>
@@ -766,13 +766,13 @@
         <v>2.546</v>
       </c>
       <c r="S4" t="n">
-        <v>-1.1457</v>
+        <v>-0.5177</v>
       </c>
       <c r="T4" t="n">
-        <v>-1.0516</v>
+        <v>-0.7711</v>
       </c>
       <c r="U4" t="n">
-        <v>-0.09420000000000001</v>
+        <v>0.2533</v>
       </c>
       <c r="V4" t="n">
         <v>1.8249</v>
@@ -787,7 +787,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A. ALVAREZ JORGE</t>
+          <t>H. REY PEREZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,73 +799,73 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>1.4013</v>
+        <v>1.7342</v>
       </c>
       <c r="E5" t="n">
-        <v>1.6263</v>
+        <v>0.8671</v>
       </c>
       <c r="F5" t="n">
-        <v>-0.225</v>
+        <v>0.8672</v>
       </c>
       <c r="G5" t="n">
-        <v>0.8014</v>
+        <v>0.4031</v>
       </c>
       <c r="H5" t="n">
-        <v>0.9326</v>
+        <v>1.4495</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.1313</v>
+        <v>-1.0463</v>
       </c>
       <c r="J5" t="n">
-        <v>1.0003</v>
+        <v>1.3292</v>
       </c>
       <c r="K5" t="n">
-        <v>1.0003</v>
+        <v>1.9921</v>
       </c>
       <c r="L5" t="n">
-        <v>0</v>
+        <v>-0.663</v>
       </c>
       <c r="M5" t="n">
-        <v>-0.199</v>
+        <v>-0.9261</v>
       </c>
       <c r="N5" t="n">
-        <v>-0.0677</v>
+        <v>-0.5427</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.1313</v>
+        <v>-0.3834</v>
       </c>
       <c r="P5" t="n">
-        <v>0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q5" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>0.1958</v>
+        <v>1.5668</v>
       </c>
       <c r="S5" t="n">
-        <v>0.0711</v>
+        <v>0.1353</v>
       </c>
       <c r="T5" t="n">
-        <v>0.0176</v>
+        <v>-0.0912</v>
       </c>
       <c r="U5" t="n">
-        <v>0.0535</v>
+        <v>0.2264</v>
       </c>
       <c r="V5" t="n">
-        <v>0.3329</v>
+        <v>0.6083</v>
       </c>
       <c r="W5" t="n">
         <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.2754</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>H. REY PEREZ</t>
+          <t>A. ALVAREZ JORGE</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -877,67 +877,67 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>1.154</v>
+        <v>1.5838</v>
       </c>
       <c r="E6" t="n">
-        <v>0.5007</v>
+        <v>1.7286</v>
       </c>
       <c r="F6" t="n">
-        <v>0.6533</v>
+        <v>-0.1448</v>
       </c>
       <c r="G6" t="n">
-        <v>0.4031</v>
+        <v>0.8014</v>
       </c>
       <c r="H6" t="n">
-        <v>1.4495</v>
+        <v>0.9326</v>
       </c>
       <c r="I6" t="n">
-        <v>-1.0463</v>
+        <v>-0.1313</v>
       </c>
       <c r="J6" t="n">
-        <v>1.3292</v>
+        <v>1.0003</v>
       </c>
       <c r="K6" t="n">
-        <v>1.9921</v>
+        <v>1.0003</v>
       </c>
       <c r="L6" t="n">
-        <v>-0.663</v>
+        <v>0</v>
       </c>
       <c r="M6" t="n">
-        <v>-0.9261</v>
+        <v>-0.199</v>
       </c>
       <c r="N6" t="n">
-        <v>-0.5427</v>
+        <v>-0.0677</v>
       </c>
       <c r="O6" t="n">
-        <v>-0.3834</v>
+        <v>-0.1313</v>
       </c>
       <c r="P6" t="n">
-        <v>0.5875</v>
+        <v>0.1958</v>
       </c>
       <c r="Q6" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="R6" t="n">
-        <v>1.5668</v>
+        <v>0.1958</v>
       </c>
       <c r="S6" t="n">
-        <v>-0.445</v>
+        <v>0.2536</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.4576</v>
+        <v>0.12</v>
       </c>
       <c r="U6" t="n">
-        <v>0.0126</v>
+        <v>0.1337</v>
       </c>
       <c r="V6" t="n">
-        <v>0.6083</v>
+        <v>0.3329</v>
       </c>
       <c r="W6" t="n">
         <v>0.6083</v>
       </c>
       <c r="X6" t="n">
-        <v>0</v>
+        <v>-0.2754</v>
       </c>
     </row>
     <row r="7">
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0161</v>
+        <v>0.8115</v>
       </c>
       <c r="E7" t="n">
-        <v>2.0318</v>
+        <v>2.5599</v>
       </c>
       <c r="F7" t="n">
-        <v>-2.0157</v>
+        <v>-1.7484</v>
       </c>
       <c r="G7" t="n">
         <v>1.5145</v>
@@ -1000,13 +1000,13 @@
         <v>0.5875</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.594</v>
+        <v>0.2014</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.7546</v>
+        <v>-0.2264</v>
       </c>
       <c r="U7" t="n">
-        <v>0.1606</v>
+        <v>0.4279</v>
       </c>
       <c r="V7" t="n">
         <v>-1.492</v>
@@ -1033,13 +1033,13 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>0.0039</v>
+        <v>0.4715</v>
       </c>
       <c r="E8" t="n">
-        <v>0.2977</v>
+        <v>0.5782</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.2938</v>
+        <v>-0.1067</v>
       </c>
       <c r="G8" t="n">
         <v>1.2797</v>
@@ -1078,13 +1078,13 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.3922</v>
+        <v>0.07539999999999999</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.6664</v>
+        <v>-0.3858</v>
       </c>
       <c r="U8" t="n">
-        <v>0.2741</v>
+        <v>0.4613</v>
       </c>
       <c r="V8" t="n">
         <v>-0.8837</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>M. OLOWOKERE</t>
+          <t>Y. MENDÉZ POLLÁN</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,64 +1111,64 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-0.9641999999999999</v>
+        <v>-0.9456</v>
       </c>
       <c r="E9" t="n">
-        <v>-1.0302</v>
+        <v>0.2793</v>
       </c>
       <c r="F9" t="n">
-        <v>0.066</v>
+        <v>-1.2249</v>
       </c>
       <c r="G9" t="n">
-        <v>-0.3166</v>
+        <v>-0.0473</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0527</v>
+        <v>-0.0473</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.3693</v>
+        <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>1.2095</v>
+        <v>0.0204</v>
       </c>
       <c r="K9" t="n">
-        <v>1.3422</v>
+        <v>0.0204</v>
       </c>
       <c r="L9" t="n">
-        <v>-0.1327</v>
+        <v>0</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.526</v>
+        <v>-0.0677</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.2895</v>
+        <v>-0.0677</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2366</v>
+        <v>0</v>
       </c>
       <c r="P9" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q9" t="n">
-        <v>-2.1543</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>2.546</v>
+        <v>0</v>
       </c>
       <c r="S9" t="n">
-        <v>0.1773</v>
+        <v>0.0429</v>
       </c>
       <c r="T9" t="n">
-        <v>-0.0853</v>
+        <v>-0.0165</v>
       </c>
       <c r="U9" t="n">
-        <v>0.2626</v>
+        <v>0.0594</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2166</v>
+        <v>-0.9412</v>
       </c>
       <c r="W9" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X9" t="n">
         <v>-1.2166</v>
@@ -1177,7 +1177,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Y. MENDÉZ POLLÁN</t>
+          <t>M. OLOWOKERE</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,64 +1189,64 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.0479</v>
+        <v>-1.0023</v>
       </c>
       <c r="E10" t="n">
-        <v>0.177</v>
+        <v>-1.2019</v>
       </c>
       <c r="F10" t="n">
-        <v>-1.2249</v>
+        <v>0.1997</v>
       </c>
       <c r="G10" t="n">
-        <v>-0.0473</v>
+        <v>-0.3166</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0473</v>
+        <v>0.0527</v>
       </c>
       <c r="I10" t="n">
-        <v>0</v>
+        <v>-0.3693</v>
       </c>
       <c r="J10" t="n">
-        <v>0.0204</v>
+        <v>1.2095</v>
       </c>
       <c r="K10" t="n">
-        <v>0.0204</v>
+        <v>1.3422</v>
       </c>
       <c r="L10" t="n">
-        <v>0</v>
+        <v>-0.1327</v>
       </c>
       <c r="M10" t="n">
-        <v>-0.0677</v>
+        <v>-1.526</v>
       </c>
       <c r="N10" t="n">
-        <v>-0.0677</v>
+        <v>-1.2895</v>
       </c>
       <c r="O10" t="n">
-        <v>0</v>
+        <v>-0.2366</v>
       </c>
       <c r="P10" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q10" t="n">
-        <v>0</v>
+        <v>-2.1543</v>
       </c>
       <c r="R10" t="n">
-        <v>0</v>
+        <v>2.546</v>
       </c>
       <c r="S10" t="n">
-        <v>-0.0594</v>
+        <v>0.1392</v>
       </c>
       <c r="T10" t="n">
-        <v>-0.1188</v>
+        <v>-0.257</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0594</v>
+        <v>0.3963</v>
       </c>
       <c r="V10" t="n">
-        <v>-0.9412</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X10" t="n">
         <v>-1.2166</v>
@@ -1255,7 +1255,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>A. FILGUEIRA BUCETA</t>
+          <t>R. PULLEIRO GONZALEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,73 +1267,73 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-1.5309</v>
+        <v>-1.6843</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.4887</v>
+        <v>-0.2553</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.0422</v>
+        <v>-1.4291</v>
       </c>
       <c r="G11" t="n">
-        <v>0.397</v>
+        <v>-0.4083</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.6241</v>
+        <v>-0.4083</v>
       </c>
       <c r="I11" t="n">
-        <v>1.0211</v>
+        <v>0</v>
       </c>
       <c r="J11" t="n">
-        <v>1.522</v>
+        <v>0</v>
       </c>
       <c r="K11" t="n">
-        <v>-0.0137</v>
+        <v>0</v>
       </c>
       <c r="L11" t="n">
-        <v>1.5358</v>
+        <v>0</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.125</v>
+        <v>-0.4083</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.4083</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5145999999999999</v>
+        <v>0</v>
       </c>
       <c r="P11" t="n">
-        <v>-0.9792</v>
+        <v>0</v>
       </c>
       <c r="Q11" t="n">
-        <v>-2.1543</v>
+        <v>-0.1958</v>
       </c>
       <c r="R11" t="n">
-        <v>1.1751</v>
+        <v>0.1958</v>
       </c>
       <c r="S11" t="n">
-        <v>1.4845</v>
+        <v>-0.0594</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.1317</v>
+        <v>-0.0594</v>
       </c>
       <c r="U11" t="n">
-        <v>1.6163</v>
+        <v>0</v>
       </c>
       <c r="V11" t="n">
-        <v>-2.4332</v>
+        <v>-1.2166</v>
       </c>
       <c r="W11" t="n">
-        <v>0.2754</v>
+        <v>0</v>
       </c>
       <c r="X11" t="n">
-        <v>-2.7086</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>R. PULLEIRO GONZALEZ</t>
+          <t>A. FILGUEIRA BUCETA</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -1345,67 +1345,67 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-1.8031</v>
+        <v>-2.1887</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.3741</v>
+        <v>-0.5316</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4291</v>
+        <v>-1.657</v>
       </c>
       <c r="G12" t="n">
-        <v>-0.4083</v>
+        <v>0.397</v>
       </c>
       <c r="H12" t="n">
-        <v>-0.4083</v>
+        <v>-0.6241</v>
       </c>
       <c r="I12" t="n">
-        <v>0</v>
+        <v>1.0211</v>
       </c>
       <c r="J12" t="n">
-        <v>0</v>
+        <v>1.522</v>
       </c>
       <c r="K12" t="n">
-        <v>0</v>
+        <v>-0.0137</v>
       </c>
       <c r="L12" t="n">
-        <v>0</v>
+        <v>1.5358</v>
       </c>
       <c r="M12" t="n">
-        <v>-0.4083</v>
+        <v>-1.125</v>
       </c>
       <c r="N12" t="n">
-        <v>-0.4083</v>
+        <v>-0.6104000000000001</v>
       </c>
       <c r="O12" t="n">
-        <v>0</v>
+        <v>-0.5145999999999999</v>
       </c>
       <c r="P12" t="n">
-        <v>0</v>
+        <v>-0.9792</v>
       </c>
       <c r="Q12" t="n">
-        <v>-0.1958</v>
+        <v>-2.1543</v>
       </c>
       <c r="R12" t="n">
-        <v>0.1958</v>
+        <v>1.1751</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.1782</v>
+        <v>0.8268</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.1782</v>
+        <v>-0.1747</v>
       </c>
       <c r="U12" t="n">
-        <v>0</v>
+        <v>1.0015</v>
       </c>
       <c r="V12" t="n">
-        <v>-1.2166</v>
+        <v>-2.4332</v>
       </c>
       <c r="W12" t="n">
-        <v>0</v>
+        <v>0.2754</v>
       </c>
       <c r="X12" t="n">
-        <v>-1.2166</v>
+        <v>-2.7086</v>
       </c>
     </row>
     <row r="13">
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-3.7508</v>
+        <v>-3.5936</v>
       </c>
       <c r="E13" t="n">
-        <v>-1.6002</v>
+        <v>-1.3362</v>
       </c>
       <c r="F13" t="n">
-        <v>-2.1505</v>
+        <v>-2.2575</v>
       </c>
       <c r="G13" t="n">
         <v>-2.2469</v>
@@ -1468,13 +1468,13 @@
         <v>0</v>
       </c>
       <c r="S13" t="n">
-        <v>-0.0119</v>
+        <v>0.1453</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.297</v>
+        <v>-0.0329</v>
       </c>
       <c r="U13" t="n">
-        <v>0.2851</v>
+        <v>0.1782</v>
       </c>
       <c r="V13" t="n">
         <v>-1.492</v>
@@ -1501,19 +1501,19 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>6.938499999999999</v>
+        <v>8.126199999999999</v>
       </c>
       <c r="E14" t="n">
-        <v>6.5912</v>
+        <v>7.779100000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>0.3473000000000006</v>
+        <v>0.3474000000000008</v>
       </c>
       <c r="G14" t="n">
-        <v>8.093300000000001</v>
+        <v>8.093299999999999</v>
       </c>
       <c r="H14" t="n">
-        <v>2.031</v>
+        <v>2.031000000000001</v>
       </c>
       <c r="I14" t="n">
         <v>6.062099999999999</v>
@@ -1522,7 +1522,7 @@
         <v>17.0309</v>
       </c>
       <c r="K14" t="n">
-        <v>9.155399999999998</v>
+        <v>9.1554</v>
       </c>
       <c r="L14" t="n">
         <v>7.875299999999999</v>
@@ -1546,13 +1546,13 @@
         <v>14.6884</v>
       </c>
       <c r="S14" t="n">
-        <v>1.0675</v>
+        <v>2.2555</v>
       </c>
       <c r="T14" t="n">
-        <v>-3.3643</v>
+        <v>-2.1762</v>
       </c>
       <c r="U14" t="n">
-        <v>4.4316</v>
+        <v>4.431800000000001</v>
       </c>
       <c r="V14" t="n">
         <v>-3.2018</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>6.8009</v>
+        <v>7.0065</v>
       </c>
       <c r="E15" t="n">
-        <v>7.7568</v>
+        <v>8.063800000000001</v>
       </c>
       <c r="F15" t="n">
-        <v>-0.9559</v>
+        <v>-1.0572</v>
       </c>
       <c r="G15" t="n">
         <v>1.1732</v>
@@ -1624,13 +1624,13 @@
         <v>1.9585</v>
       </c>
       <c r="S15" t="n">
-        <v>0.1375</v>
+        <v>0.3432</v>
       </c>
       <c r="T15" t="n">
-        <v>-0.9745</v>
+        <v>-0.6675</v>
       </c>
       <c r="U15" t="n">
-        <v>1.1121</v>
+        <v>1.0107</v>
       </c>
       <c r="V15" t="n">
         <v>5.686</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>3.2161</v>
+        <v>2.9829</v>
       </c>
       <c r="E16" t="n">
-        <v>1.1829</v>
+        <v>1.0806</v>
       </c>
       <c r="F16" t="n">
-        <v>2.0332</v>
+        <v>1.9023</v>
       </c>
       <c r="G16" t="n">
         <v>-0.2848</v>
@@ -1702,13 +1702,13 @@
         <v>1.1751</v>
       </c>
       <c r="S16" t="n">
-        <v>0.517</v>
+        <v>0.2838</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.31</v>
+        <v>-0.4123</v>
       </c>
       <c r="U16" t="n">
-        <v>0.8269</v>
+        <v>0.6961000000000001</v>
       </c>
       <c r="V16" t="n">
         <v>2.9839</v>
@@ -1735,13 +1735,13 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.4581</v>
+        <v>2.3069</v>
       </c>
       <c r="E17" t="n">
-        <v>1.9128</v>
+        <v>1.7081</v>
       </c>
       <c r="F17" t="n">
-        <v>0.5454</v>
+        <v>0.5988</v>
       </c>
       <c r="G17" t="n">
         <v>1.4061</v>
@@ -1780,13 +1780,13 @@
         <v>1.3709</v>
       </c>
       <c r="S17" t="n">
-        <v>0.9137</v>
+        <v>0.7625</v>
       </c>
       <c r="T17" t="n">
-        <v>0.4623</v>
+        <v>0.2576</v>
       </c>
       <c r="U17" t="n">
-        <v>0.4515</v>
+        <v>0.5049</v>
       </c>
       <c r="V17" t="n">
         <v>-0.0576</v>
@@ -1813,13 +1813,13 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.5543</v>
+        <v>-1.2307</v>
       </c>
       <c r="E18" t="n">
         <v>-0.1</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.4542</v>
+        <v>-1.1307</v>
       </c>
       <c r="G18" t="n">
         <v>-0.9872</v>
@@ -1858,13 +1858,13 @@
         <v>0.7834</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.7422</v>
+        <v>-0.4186</v>
       </c>
       <c r="T18" t="n">
         <v>-0.4576</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.2846</v>
+        <v>0.039</v>
       </c>
       <c r="V18" t="n">
         <v>-0.6083</v>
@@ -1891,13 +1891,13 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>-1.5869</v>
+        <v>-1.4237</v>
       </c>
       <c r="E19" t="n">
         <v>-0.0742</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.5127</v>
+        <v>-1.3495</v>
       </c>
       <c r="G19" t="n">
         <v>-1.0737</v>
@@ -1936,13 +1936,13 @@
         <v>0.9792</v>
       </c>
       <c r="S19" t="n">
-        <v>-0.3915</v>
+        <v>-0.2283</v>
       </c>
       <c r="T19" t="n">
         <v>-0.5764</v>
       </c>
       <c r="U19" t="n">
-        <v>0.1849</v>
+        <v>0.348</v>
       </c>
       <c r="V19" t="n">
         <v>-0.1217</v>
@@ -1957,7 +1957,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>A. RODRIGUEZ FERNANDEZ</t>
+          <t>P. SABUGUEIRO ABEIJÓN</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,73 +1969,73 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.7697</v>
+        <v>-1.7866</v>
       </c>
       <c r="E20" t="n">
-        <v>-0.3831</v>
+        <v>0.2782</v>
       </c>
       <c r="F20" t="n">
-        <v>-1.3865</v>
+        <v>-2.0648</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.8166</v>
+        <v>0.7089</v>
       </c>
       <c r="H20" t="n">
-        <v>-1.0391</v>
+        <v>0.2943</v>
       </c>
       <c r="I20" t="n">
-        <v>0.2225</v>
+        <v>0.4145</v>
       </c>
       <c r="J20" t="n">
-        <v>1.3813</v>
+        <v>2.3797</v>
       </c>
       <c r="K20" t="n">
-        <v>0.114</v>
+        <v>1.0412</v>
       </c>
       <c r="L20" t="n">
-        <v>1.2673</v>
+        <v>1.3385</v>
       </c>
       <c r="M20" t="n">
-        <v>-2.1979</v>
+        <v>-1.6708</v>
       </c>
       <c r="N20" t="n">
-        <v>-1.153</v>
+        <v>-0.7468</v>
       </c>
       <c r="O20" t="n">
-        <v>-1.0449</v>
+        <v>-0.924</v>
       </c>
       <c r="P20" t="n">
-        <v>-0.1958</v>
+        <v>0.9792</v>
       </c>
       <c r="Q20" t="n">
-        <v>-2.1543</v>
+        <v>-0.9792</v>
       </c>
       <c r="R20" t="n">
         <v>1.9585</v>
       </c>
       <c r="S20" t="n">
-        <v>0.5810999999999999</v>
+        <v>-0.3757</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3899</v>
+        <v>-0.4564</v>
       </c>
       <c r="U20" t="n">
-        <v>0.1911</v>
+        <v>0.08069999999999999</v>
       </c>
       <c r="V20" t="n">
-        <v>-1.3383</v>
+        <v>-3.0991</v>
       </c>
       <c r="W20" t="n">
-        <v>0</v>
+        <v>-0.6659</v>
       </c>
       <c r="X20" t="n">
-        <v>-1.3383</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>P. SABUGUEIRO ABEIJÓN</t>
+          <t>A. RODRIGUEZ FERNANDEZ</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -2047,67 +2047,67 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>-2.183</v>
+        <v>-1.9799</v>
       </c>
       <c r="E21" t="n">
-        <v>0.1758</v>
+        <v>-0.9971</v>
       </c>
       <c r="F21" t="n">
-        <v>-2.3588</v>
+        <v>-0.9828</v>
       </c>
       <c r="G21" t="n">
-        <v>0.7089</v>
+        <v>-0.8166</v>
       </c>
       <c r="H21" t="n">
-        <v>0.2943</v>
+        <v>-1.0391</v>
       </c>
       <c r="I21" t="n">
-        <v>0.4145</v>
+        <v>0.2225</v>
       </c>
       <c r="J21" t="n">
-        <v>2.3797</v>
+        <v>1.3813</v>
       </c>
       <c r="K21" t="n">
-        <v>1.0412</v>
+        <v>0.114</v>
       </c>
       <c r="L21" t="n">
-        <v>1.3385</v>
+        <v>1.2673</v>
       </c>
       <c r="M21" t="n">
-        <v>-1.6708</v>
+        <v>-2.1979</v>
       </c>
       <c r="N21" t="n">
-        <v>-0.7468</v>
+        <v>-1.153</v>
       </c>
       <c r="O21" t="n">
-        <v>-0.924</v>
+        <v>-1.0449</v>
       </c>
       <c r="P21" t="n">
-        <v>0.9792</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q21" t="n">
-        <v>-0.9792</v>
+        <v>-2.1543</v>
       </c>
       <c r="R21" t="n">
         <v>1.9585</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.772</v>
+        <v>0.3708</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.5587</v>
+        <v>-0.2241</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.2133</v>
+        <v>0.5949</v>
       </c>
       <c r="V21" t="n">
-        <v>-3.0991</v>
+        <v>-1.3383</v>
       </c>
       <c r="W21" t="n">
-        <v>-0.6659</v>
+        <v>0</v>
       </c>
       <c r="X21" t="n">
-        <v>-2.4332</v>
+        <v>-1.3383</v>
       </c>
     </row>
     <row r="22">
@@ -2125,13 +2125,13 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-3.2019</v>
+        <v>-2.9428</v>
       </c>
       <c r="E22" t="n">
-        <v>-4.0934</v>
+        <v>-3.7864</v>
       </c>
       <c r="F22" t="n">
-        <v>0.8914</v>
+        <v>0.8436</v>
       </c>
       <c r="G22" t="n">
         <v>-5.3095</v>
@@ -2170,13 +2170,13 @@
         <v>1.9585</v>
       </c>
       <c r="S22" t="n">
-        <v>0.3449</v>
+        <v>0.604</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.8557</v>
+        <v>-0.5487</v>
       </c>
       <c r="U22" t="n">
-        <v>1.2006</v>
+        <v>1.1528</v>
       </c>
       <c r="V22" t="n">
         <v>0</v>
@@ -2203,13 +2203,13 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-3.2526</v>
+        <v>-3.2839</v>
       </c>
       <c r="E23" t="n">
-        <v>-3.2392</v>
+        <v>-3.1369</v>
       </c>
       <c r="F23" t="n">
-        <v>-0.0134</v>
+        <v>-0.147</v>
       </c>
       <c r="G23" t="n">
         <v>-2.2055</v>
@@ -2248,13 +2248,13 @@
         <v>0.3917</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.3379</v>
+        <v>-0.3692</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.517</v>
+        <v>-0.4146</v>
       </c>
       <c r="U23" t="n">
-        <v>0.1791</v>
+        <v>0.0454</v>
       </c>
       <c r="V23" t="n">
         <v>-0.1217</v>
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-5.8651</v>
+        <v>-5.2226</v>
       </c>
       <c r="E24" t="n">
-        <v>-3.4856</v>
+        <v>-3.3833</v>
       </c>
       <c r="F24" t="n">
-        <v>-2.3795</v>
+        <v>-1.8393</v>
       </c>
       <c r="G24" t="n">
         <v>-0.7043</v>
@@ -2326,13 +2326,13 @@
         <v>1.1751</v>
       </c>
       <c r="S24" t="n">
-        <v>-1.318</v>
+        <v>-0.6755</v>
       </c>
       <c r="T24" t="n">
-        <v>-1.0339</v>
+        <v>-0.9316</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.2841</v>
+        <v>0.2561</v>
       </c>
       <c r="V24" t="n">
         <v>-0.1217</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-6.938400000000001</v>
+        <v>-5.573899999999999</v>
       </c>
       <c r="E25" t="n">
-        <v>-0.3471999999999995</v>
+        <v>-0.3471999999999991</v>
       </c>
       <c r="F25" t="n">
-        <v>-6.591</v>
+        <v>-5.226599999999999</v>
       </c>
       <c r="G25" t="n">
         <v>-8.093400000000001</v>
@@ -2383,7 +2383,7 @@
         <v>7.1246</v>
       </c>
       <c r="L25" t="n">
-        <v>1.813099999999999</v>
+        <v>1.8131</v>
       </c>
       <c r="M25" t="n">
         <v>-17.0309</v>
@@ -2404,13 +2404,13 @@
         <v>13.7094</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.0674</v>
+        <v>0.2969999999999999</v>
       </c>
       <c r="T25" t="n">
         <v>-4.4316</v>
       </c>
       <c r="U25" t="n">
-        <v>3.3642</v>
+        <v>4.7286</v>
       </c>
       <c r="V25" t="n">
         <v>3.201499999999999</v>
@@ -2419,7 +2419,7 @@
         <v>9.8354</v>
       </c>
       <c r="X25" t="n">
-        <v>-6.633899999999999</v>
+        <v>-6.6339</v>
       </c>
     </row>
   </sheetData>
